--- a/outputs/etf_trend_strategy/threshold_0.9/backtests/window_15/return_vol/post_rank_positive_return_rsi_bias_filter/staggered_10d/rsi_10_gt_60__bias_15_gt_-0.02/next_day_vwap/next_day_vwap_annual_metrics.xlsx
+++ b/outputs/etf_trend_strategy/threshold_0.9/backtests/window_15/return_vol/post_rank_positive_return_rsi_bias_filter/staggered_10d/rsi_10_gt_60__bias_15_gt_-0.02/next_day_vwap/next_day_vwap_annual_metrics.xlsx
@@ -466,13 +466,13 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
-    <col width="23" customWidth="1" min="2" max="2"/>
+    <col width="22" customWidth="1" min="2" max="2"/>
     <col width="23" customWidth="1" min="3" max="3"/>
-    <col width="22" customWidth="1" min="4" max="4"/>
+    <col width="23" customWidth="1" min="4" max="4"/>
     <col width="21" customWidth="1" min="5" max="5"/>
     <col width="21" customWidth="1" min="6" max="6"/>
     <col width="21" customWidth="1" min="7" max="7"/>
-    <col width="22" customWidth="1" min="8" max="8"/>
+    <col width="21" customWidth="1" min="8" max="8"/>
     <col width="21" customWidth="1" min="9" max="9"/>
     <col width="21" customWidth="1" min="10" max="10"/>
     <col width="21" customWidth="1" min="11" max="11"/>
@@ -560,43 +560,43 @@
         </is>
       </c>
       <c r="B2" s="3" t="n">
-        <v>0.004705147818917066</v>
+        <v>0.01050280562350769</v>
       </c>
       <c r="C2" s="3" t="n">
         <v>-0.02176047699359285</v>
       </c>
       <c r="D2" s="3" t="n">
-        <v>0.02705434015911701</v>
+        <v>0.03298096412823925</v>
       </c>
       <c r="E2" s="3" t="n">
-        <v>0.2572944792714901</v>
+        <v>0.2534802336681333</v>
       </c>
       <c r="F2" s="3" t="n">
-        <v>0.224853036313872</v>
+        <v>0.2451479902572316</v>
       </c>
       <c r="G2" s="4" t="n">
-        <v>0.09077737969630727</v>
+        <v>0.1140713865013064</v>
       </c>
       <c r="H2" s="4" t="n">
-        <v>0.1306821850883682</v>
+        <v>0.1638046165382875</v>
       </c>
       <c r="I2" s="4" t="n">
-        <v>0.2088854587589049</v>
+        <v>0.2142658916161102</v>
       </c>
       <c r="J2" s="3" t="n">
-        <v>0.1624379950230933</v>
+        <v>0.2049456285623197</v>
       </c>
       <c r="K2" s="3" t="n">
         <v>0.1506490308477421</v>
       </c>
       <c r="L2" s="3" t="n">
-        <v>0.1483449418676852</v>
+        <v>0.1927326650045388</v>
       </c>
       <c r="M2" s="4" t="n">
-        <v>0.03274266285595107</v>
+        <v>0.05795059966529306</v>
       </c>
       <c r="N2" s="5" t="n">
-        <v>18.72997709896923</v>
+        <v>14.53574194939961</v>
       </c>
     </row>
     <row r="3">
@@ -606,43 +606,43 @@
         </is>
       </c>
       <c r="B3" s="3" t="n">
-        <v>-0.1624876928089868</v>
+        <v>-0.1339218675784142</v>
       </c>
       <c r="C3" s="3" t="n">
         <v>-0.2255774308756096</v>
       </c>
       <c r="D3" s="3" t="n">
-        <v>0.08146681228306085</v>
+        <v>0.1183534247985925</v>
       </c>
       <c r="E3" s="3" t="n">
-        <v>0.1912586859808239</v>
+        <v>0.1817545736995043</v>
       </c>
       <c r="F3" s="3" t="n">
-        <v>0.1832247505720045</v>
+        <v>0.1813423499092467</v>
       </c>
       <c r="G3" s="4" t="n">
-        <v>-0.9479034289291399</v>
+        <v>-0.814674549535812</v>
       </c>
       <c r="H3" s="4" t="n">
-        <v>-1.329499256841476</v>
+        <v>-1.094067357390069</v>
       </c>
       <c r="I3" s="4" t="n">
-        <v>0.4255919350062463</v>
+        <v>0.6132208774818204</v>
       </c>
       <c r="J3" s="3" t="n">
-        <v>0.2103081260698296</v>
+        <v>0.1817163204353401</v>
       </c>
       <c r="K3" s="3" t="n">
         <v>0.2845881262232945</v>
       </c>
       <c r="L3" s="3" t="n">
-        <v>0.1141864555899774</v>
+        <v>0.1010942053852248</v>
       </c>
       <c r="M3" s="4" t="n">
-        <v>-0.8016900056935707</v>
+        <v>-0.7652161690522228</v>
       </c>
       <c r="N3" s="5" t="n">
-        <v>16.81323633435534</v>
+        <v>12.01684943378021</v>
       </c>
     </row>
     <row r="4">
@@ -652,43 +652,43 @@
         </is>
       </c>
       <c r="B4" s="3" t="n">
-        <v>0.01573233246987549</v>
+        <v>-0.1581942381014702</v>
       </c>
       <c r="C4" s="3" t="n">
         <v>-0.1141699148043651</v>
       </c>
       <c r="D4" s="3" t="n">
-        <v>0.1466446550475311</v>
+        <v>-0.04969838350814371</v>
       </c>
       <c r="E4" s="3" t="n">
-        <v>0.2210241057336413</v>
+        <v>0.1552431287835689</v>
       </c>
       <c r="F4" s="3" t="n">
-        <v>0.1955927911322725</v>
+        <v>0.1370664115453247</v>
       </c>
       <c r="G4" s="4" t="n">
-        <v>0.1156417214001881</v>
+        <v>-1.172989379456593</v>
       </c>
       <c r="H4" s="4" t="n">
-        <v>0.1806048787318857</v>
+        <v>-1.545768836289088</v>
       </c>
       <c r="I4" s="4" t="n">
-        <v>0.8054387815880714</v>
+        <v>-0.3656631074867872</v>
       </c>
       <c r="J4" s="3" t="n">
-        <v>0.1873844708533803</v>
+        <v>0.2150783669908414</v>
       </c>
       <c r="K4" s="3" t="n">
         <v>0.2177913835362562</v>
       </c>
       <c r="L4" s="3" t="n">
-        <v>0.07660751123815934</v>
+        <v>0.08993127056888794</v>
       </c>
       <c r="M4" s="4" t="n">
-        <v>0.08745509854759219</v>
+        <v>-0.763271662352301</v>
       </c>
       <c r="N4" s="5" t="n">
-        <v>18.17417709821747</v>
+        <v>12.50219787475997</v>
       </c>
     </row>
     <row r="5">
@@ -698,43 +698,43 @@
         </is>
       </c>
       <c r="B5" s="3" t="n">
-        <v>-0.06200126830968666</v>
+        <v>-0.04160093891283423</v>
       </c>
       <c r="C5" s="3" t="n">
         <v>0.1298071537204202</v>
       </c>
       <c r="D5" s="3" t="n">
-        <v>-0.1697709395789255</v>
+        <v>-0.1517144692072577</v>
       </c>
       <c r="E5" s="3" t="n">
-        <v>0.2051231252223124</v>
+        <v>0.1876418807382159</v>
       </c>
       <c r="F5" s="3" t="n">
-        <v>0.1597631601217326</v>
+        <v>0.147887776512847</v>
       </c>
       <c r="G5" s="4" t="n">
-        <v>-0.2952400143210483</v>
+        <v>-0.2216621451302079</v>
       </c>
       <c r="H5" s="4" t="n">
-        <v>-0.4158173445894771</v>
+        <v>-0.3171931172807131</v>
       </c>
       <c r="I5" s="4" t="n">
-        <v>-1.241934932653994</v>
+        <v>-1.213406551306628</v>
       </c>
       <c r="J5" s="3" t="n">
-        <v>0.2054789615419516</v>
+        <v>0.1816555687737573</v>
       </c>
       <c r="K5" s="3" t="n">
         <v>0.1515696200238076</v>
       </c>
       <c r="L5" s="3" t="n">
-        <v>0.2862022742346274</v>
+        <v>0.2519169051362038</v>
       </c>
       <c r="M5" s="4" t="n">
-        <v>-0.3137980970237738</v>
+        <v>-0.2382654514080488</v>
       </c>
       <c r="N5" s="5" t="n">
-        <v>17.54334278056461</v>
+        <v>13.02150234319933</v>
       </c>
     </row>
     <row r="6">
@@ -744,43 +744,43 @@
         </is>
       </c>
       <c r="B6" s="3" t="n">
-        <v>0.3455036445696471</v>
+        <v>0.09357473016548612</v>
       </c>
       <c r="C6" s="3" t="n">
         <v>0.2243203183030871</v>
       </c>
       <c r="D6" s="3" t="n">
-        <v>0.09898008262618596</v>
+        <v>-0.1067903441468774</v>
       </c>
       <c r="E6" s="3" t="n">
-        <v>0.2623869188282677</v>
+        <v>0.155721912610383</v>
       </c>
       <c r="F6" s="3" t="n">
-        <v>0.1783983443770497</v>
+        <v>0.1095729021818439</v>
       </c>
       <c r="G6" s="4" t="n">
-        <v>1.248118337849301</v>
+        <v>0.5781392770349633</v>
       </c>
       <c r="H6" s="4" t="n">
-        <v>1.791409038158437</v>
+        <v>0.7796879297544448</v>
       </c>
       <c r="I6" s="4" t="n">
-        <v>0.6635129197593934</v>
+        <v>-1.086868763143371</v>
       </c>
       <c r="J6" s="3" t="n">
-        <v>0.1991352421460021</v>
+        <v>0.08893301347318128</v>
       </c>
       <c r="K6" s="3" t="n">
         <v>0.1188658802983931</v>
       </c>
       <c r="L6" s="3" t="n">
-        <v>0.1719478820005027</v>
+        <v>0.1692839597273365</v>
       </c>
       <c r="M6" s="4" t="n">
-        <v>1.80969583286075</v>
+        <v>1.093000047376227</v>
       </c>
       <c r="N6" s="5" t="n">
-        <v>20.65048871364281</v>
+        <v>13.76424999272688</v>
       </c>
     </row>
     <row r="7">
@@ -790,43 +790,43 @@
         </is>
       </c>
       <c r="B7" s="3" t="n">
-        <v>0.04339576713685411</v>
+        <v>0.08040676748875697</v>
       </c>
       <c r="C7" s="3" t="n">
         <v>-0.01504143451691176</v>
       </c>
       <c r="D7" s="3" t="n">
-        <v>0.05932960400735721</v>
+        <v>0.09690580431558793</v>
       </c>
       <c r="E7" s="3" t="n">
-        <v>0.3629195223478967</v>
+        <v>0.2853262130019728</v>
       </c>
       <c r="F7" s="3" t="n">
-        <v>0.2985464489456521</v>
+        <v>0.2534806495772702</v>
       </c>
       <c r="G7" s="4" t="n">
-        <v>0.3549827805196711</v>
+        <v>0.5855475296427973</v>
       </c>
       <c r="H7" s="4" t="n">
-        <v>0.4737118164311946</v>
+        <v>0.8047081852750818</v>
       </c>
       <c r="I7" s="4" t="n">
-        <v>0.4862022252091446</v>
+        <v>0.7235101619363298</v>
       </c>
       <c r="J7" s="3" t="n">
-        <v>0.2178798138910623</v>
+        <v>0.1649652198963256</v>
       </c>
       <c r="K7" s="3" t="n">
         <v>0.127969093077366</v>
       </c>
       <c r="L7" s="3" t="n">
-        <v>0.1996236086783674</v>
+        <v>0.1359268304118429</v>
       </c>
       <c r="M7" s="4" t="n">
-        <v>0.3702101562865365</v>
+        <v>0.9194906196648797</v>
       </c>
       <c r="N7" s="5" t="n">
-        <v>21.63694935759248</v>
+        <v>15.46619502140913</v>
       </c>
     </row>
   </sheetData>
